--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -273,7 +273,7 @@
 【JP Core仕様】口腔診査結果レポートのプロファイル</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
 【JP Core仕様】DiagnosticReportリソースの共通プロファイル</t>
   </si>
   <si>
@@ -941,7 +941,7 @@
 </t>
   </si>
   <si>
-    <t>依頼時におけるヘルスケアイベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+    <t>依頼時における診療イベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
   </si>
   <si>
     <t>例：診療、歯科健診（検診）、身元不明者調査 ※JP Coreに網羅されていない</t>
